--- a/RoomPilot_Docs/01_requirements/requirements_tracker.xlsx
+++ b/RoomPilot_Docs/01_requirements/requirements_tracker.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="封面"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="200">
   <si>
     <t>Gate ID</t>
   </si>
@@ -52,6 +52,15 @@
     <t>ACPT-001～003（內文見 prd.md §3.1）</t>
   </si>
   <si>
+    <t>核准</t>
+  </si>
+  <si>
+    <t>林柏彥</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
     <t>DEC-002；可觀察路徑 SCN-001～003</t>
   </si>
   <si>
@@ -76,6 +85,9 @@
     <t>ACPT-009～014（內文見 prd.md §3.3）</t>
   </si>
   <si>
+    <t>退回</t>
+  </si>
+  <si>
     <t>DEC-004；比例尺權威未定（OPEN-28）、辨識基準線待確認（OPEN-25）</t>
   </si>
   <si>
@@ -133,6 +145,9 @@
     <t>第 8 步 AI 渲染與成果包完成</t>
   </si>
   <si>
+    <t>1、2</t>
+  </si>
+  <si>
     <t>ACPT-050～055、060（內文見 prd.md §3.8）</t>
   </si>
   <si>
@@ -145,6 +160,9 @@
     <t>Pilot 驗收 Gate</t>
   </si>
   <si>
+    <t>1、3</t>
+  </si>
+  <si>
     <t>ACPT-001～060 全數通過，含跨步 ACPT-007、018～023、046、056、057</t>
   </si>
   <si>
@@ -343,9 +361,6 @@
     <t>狀態</t>
   </si>
   <si>
-    <t>核准</t>
-  </si>
-  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -370,10 +385,7 @@
     <t>ACPT-008、018、021、022、046</t>
   </si>
   <si>
-    <t>待 owner 核准</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
+    <t>已核准</t>
   </si>
   <si>
     <t>prd.md §1 專案總覽；§5 範圍與限制</t>
@@ -586,7 +598,7 @@
     <t>Pilot 驗收要跑哪些真實案例、幾間房、什麼算通過、綠燈基準線是什麼</t>
   </si>
   <si>
-    <t>ACPT-058、059（受阻：基準線未定義）</t>
+    <t>ACPT-058、059；綠燈基準線＝2026-08-12 pytest 905 passed／35 failed（owner 2026-08-12 選定），人工 UAT 本輪不計入</t>
   </si>
   <si>
     <t>prd.md §2 商業目標；§6 待辦問題與決策</t>
@@ -612,7 +624,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -622,25 +634,19 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -702,7 +708,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -710,11 +716,20 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -722,8 +737,8 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -731,8 +746,11 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1039,41 +1057,41 @@
   <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="95.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="14" width="95.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="26.25">
-      <c r="A1" s="8" t="s">
-        <v>191</v>
+      <c r="A1" s="11" t="s">
+        <v>195</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="9"/>
+      <c r="A2" s="12"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21">
-      <c r="A3" s="10" t="s">
-        <v>192</v>
+      <c r="A3" s="13" t="s">
+        <v>196</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="9"/>
+      <c r="A4" s="12"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="9" t="s">
-        <v>193</v>
+      <c r="A5" s="12" t="s">
+        <v>197</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="9"/>
+      <c r="A6" s="12"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="9" t="s">
-        <v>194</v>
+      <c r="A7" s="12" t="s">
+        <v>198</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="9" t="s">
-        <v>195</v>
+      <c r="A8" s="12" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -1089,641 +1107,717 @@
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="76.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="-0.5664285714285714" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1" hidden="1"/>
-    <col min="5" max="5" style="4" width="16.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="46.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="4" width="3.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="4" width="3.1478571428571427" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="4" width="11.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="4" width="58.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="76.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="-0.5664285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="13.576428571428572" customWidth="1" bestFit="1" hidden="1"/>
+    <col min="5" max="5" style="7" width="16.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="46.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="10" width="5.576428571428571" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="10.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="6" width="11.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="6" width="58.29071428571429" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="28" customFormat="1" s="1">
       <c r="A1" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>116</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E2" s="7">
+      <c r="A2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" s="5">
         <v>1</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="F2" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="7">
+      <c r="E4" s="5">
         <v>1</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
+      <c r="F4" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="5">
+        <v>3</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="7">
+      <c r="E16" s="5">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" s="5">
         <v>1</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" s="7">
+      <c r="F17" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" s="5">
         <v>1</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="F18" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" s="5">
         <v>1</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="F19" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="5">
         <v>1</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="7">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" s="7">
-        <v>3</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>190</v>
+      <c r="F20" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -1739,321 +1833,321 @@
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="28" customFormat="1" s="1">
       <c r="A1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
+      <c r="A2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
+      <c r="A3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
+      <c r="A4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
+      <c r="A5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
+      <c r="A6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="A7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="A8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="A9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="A10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="A11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="A12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="A13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="A14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="A15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="A16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="A17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+      <c r="A18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="A19" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2068,14 +2162,14 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="22.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="36.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="4" width="24.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="22.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="59.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="95.7192857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
@@ -2085,7 +2179,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -2104,166 +2198,238 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="5">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
+      <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
+      <c r="A4" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
+      <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
+      <c r="E5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
+      <c r="A6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
+      <c r="E6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
+      <c r="A7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3" t="s">
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
+      <c r="A8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3" t="s">
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
+      <c r="E8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
+      <c r="A9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>43</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="22.5">
+      <c r="A10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
